--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -61857,6 +61857,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2341">
+      <c r="A2341" s="1" t="n">
+        <v>45940.2916666667</v>
+      </c>
+      <c r="B2341" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2341" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F2341" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="G2341" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2341" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -61883,6 +61883,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>45943.2916666667</v>
+      </c>
+      <c r="B2342" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F2342" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="G2342" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2342" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -61909,6 +61909,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2343">
+      <c r="A2343" s="1" t="n">
+        <v>45944.2916666667</v>
+      </c>
+      <c r="B2343" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="G2343" t="s">
+        <v>222</v>
+      </c>
+      <c r="H2343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="1" t="n">
+        <v>45945.3263888889</v>
+      </c>
+      <c r="B2344" t="n">
+        <v>480</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2344" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2344" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2344" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -61937,7 +61937,7 @@
     </row>
     <row r="2344">
       <c r="A2344" s="1" t="n">
-        <v>45945.3263888889</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2344" t="n">
         <v>480</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -61961,6 +61961,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2345">
+      <c r="A2345" s="1" t="n">
+        <v>45946.2916666667</v>
+      </c>
+      <c r="B2345" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2345" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2345" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2345" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -61987,6 +61987,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2346">
+      <c r="A2346" s="1" t="n">
+        <v>45947.2916666667</v>
+      </c>
+      <c r="B2346" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2346" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2346" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62013,6 +62013,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2347">
+      <c r="A2347" s="1" t="n">
+        <v>45950.2916666667</v>
+      </c>
+      <c r="B2347" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2347" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2347" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2347" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2347" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62039,6 +62039,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2348">
+      <c r="A2348" s="1" t="n">
+        <v>45951.2916666667</v>
+      </c>
+      <c r="B2348" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2348" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2348" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2348" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62065,6 +62065,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2349">
+      <c r="A2349" s="1" t="n">
+        <v>45952.2916666667</v>
+      </c>
+      <c r="B2349" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2349" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2349" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62091,6 +62091,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2350">
+      <c r="A2350" s="1" t="n">
+        <v>45953.2916666667</v>
+      </c>
+      <c r="B2350" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2350" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2350" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62117,6 +62117,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2351">
+      <c r="A2351" s="1" t="n">
+        <v>45954.2916666667</v>
+      </c>
+      <c r="B2351" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2351" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2351" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62143,6 +62143,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2352">
+      <c r="A2352" s="1" t="n">
+        <v>45957.3333333333</v>
+      </c>
+      <c r="B2352" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="G2352" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2352" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" s="1" t="n">
+        <v>45958.5810416667</v>
+      </c>
+      <c r="B2353" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2353" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="D2353" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="E2353" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F2353" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="G2353" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2353" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62171,7 +62171,7 @@
     </row>
     <row r="2353">
       <c r="A2353" s="1" t="n">
-        <v>45958.5810416667</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2353" t="n">
         <v>3000</v>
@@ -62192,6 +62192,32 @@
         <v>152</v>
       </c>
       <c r="H2353" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="1" t="n">
+        <v>45959.5701851852</v>
+      </c>
+      <c r="B2354" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="G2354" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2354" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62197,7 +62197,7 @@
     </row>
     <row r="2354">
       <c r="A2354" s="1" t="n">
-        <v>45959.5701851852</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2354" t="n">
         <v>360</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62221,6 +62221,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2355">
+      <c r="A2355" s="1" t="n">
+        <v>45960.3333333333</v>
+      </c>
+      <c r="B2355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="G2355" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2355" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62247,6 +62247,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2356">
+      <c r="A2356" s="1" t="n">
+        <v>45961.3333333333</v>
+      </c>
+      <c r="B2356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2356" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="G2356" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2356" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" s="1" t="n">
+        <v>45964.665775463</v>
+      </c>
+      <c r="B2357" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2357" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>4.1399998664856</v>
+      </c>
+      <c r="G2357" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2357" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62275,7 +62275,7 @@
     </row>
     <row r="2357">
       <c r="A2357" s="1" t="n">
-        <v>45964.665775463</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2357" t="n">
         <v>600</v>
@@ -62296,6 +62296,32 @@
         <v>148</v>
       </c>
       <c r="H2357" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="1" t="n">
+        <v>45965.3471759259</v>
+      </c>
+      <c r="B2358" t="n">
+        <v>480</v>
+      </c>
+      <c r="C2358" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F2358" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G2358" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2358" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62301,7 +62301,7 @@
     </row>
     <row r="2358">
       <c r="A2358" s="1" t="n">
-        <v>45965.3471759259</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2358" t="n">
         <v>480</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62325,6 +62325,110 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2359">
+      <c r="A2359" s="1" t="n">
+        <v>45966.3333333333</v>
+      </c>
+      <c r="B2359" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2359" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D2359" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E2359" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F2359" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G2359" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2359" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2360" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2360" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D2360" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E2360" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F2360" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G2360" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2360" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2361" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2361" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="D2361" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E2361" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="F2361" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="G2361" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2361" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="1" t="n">
+        <v>45971.5750231482</v>
+      </c>
+      <c r="B2362" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C2362" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2362" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="E2362" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2362" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="G2362" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2362" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62405,7 +62405,7 @@
     </row>
     <row r="2362">
       <c r="A2362" s="1" t="n">
-        <v>45971.5750231482</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2362" t="n">
         <v>2040</v>
@@ -62426,6 +62426,32 @@
         <v>119</v>
       </c>
       <c r="H2362" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="1" t="n">
+        <v>45972.6108101852</v>
+      </c>
+      <c r="B2363" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C2363" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="D2363" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E2363" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F2363" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="G2363" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2363" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62431,7 +62431,7 @@
     </row>
     <row r="2363">
       <c r="A2363" s="1" t="n">
-        <v>45972.6108101852</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2363" t="n">
         <v>1920</v>
@@ -62452,6 +62452,32 @@
         <v>122</v>
       </c>
       <c r="H2363" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="1" t="n">
+        <v>45973.442974537</v>
+      </c>
+      <c r="B2364" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C2364" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="D2364" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="E2364" t="n">
+        <v>4.01999998092651</v>
+      </c>
+      <c r="F2364" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="G2364" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2364" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62457,7 +62457,7 @@
     </row>
     <row r="2364">
       <c r="A2364" s="1" t="n">
-        <v>45973.442974537</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2364" t="n">
         <v>1920</v>
@@ -62478,6 +62478,32 @@
         <v>122</v>
       </c>
       <c r="H2364" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" s="1" t="n">
+        <v>45974.5864583333</v>
+      </c>
+      <c r="B2365" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2365" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="D2365" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="E2365" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F2365" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="G2365" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2365" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62483,7 +62483,7 @@
     </row>
     <row r="2365">
       <c r="A2365" s="1" t="n">
-        <v>45974.5864583333</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2365" t="n">
         <v>120</v>
@@ -62504,6 +62504,32 @@
         <v>146</v>
       </c>
       <c r="H2365" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" s="1" t="n">
+        <v>45975.5820138889</v>
+      </c>
+      <c r="B2366" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2366" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D2366" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2366" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F2366" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="G2366" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2366" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62509,7 +62509,7 @@
     </row>
     <row r="2366">
       <c r="A2366" s="1" t="n">
-        <v>45975.5820138889</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2366" t="n">
         <v>3000</v>
@@ -62530,6 +62530,32 @@
         <v>147</v>
       </c>
       <c r="H2366" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" s="1" t="n">
+        <v>45978.6793981481</v>
+      </c>
+      <c r="B2367" t="n">
+        <v>3120</v>
+      </c>
+      <c r="C2367" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D2367" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="E2367" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F2367" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="G2367" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2367" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62535,7 +62535,7 @@
     </row>
     <row r="2367">
       <c r="A2367" s="1" t="n">
-        <v>45978.6793981481</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2367" t="n">
         <v>3120</v>
@@ -62556,6 +62556,32 @@
         <v>140</v>
       </c>
       <c r="H2367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="1" t="n">
+        <v>45979.5659953704</v>
+      </c>
+      <c r="B2368" t="n">
+        <v>240</v>
+      </c>
+      <c r="C2368" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D2368" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="E2368" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="F2368" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="G2368" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2368" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62561,7 +62561,7 @@
     </row>
     <row r="2368">
       <c r="A2368" s="1" t="n">
-        <v>45979.5659953704</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2368" t="n">
         <v>240</v>
@@ -62582,6 +62582,32 @@
         <v>140</v>
       </c>
       <c r="H2368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" s="1" t="n">
+        <v>45980.6753472222</v>
+      </c>
+      <c r="B2369" t="n">
+        <v>3120</v>
+      </c>
+      <c r="C2369" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2369" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E2369" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F2369" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2369" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2369" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62587,7 +62587,7 @@
     </row>
     <row r="2369">
       <c r="A2369" s="1" t="n">
-        <v>45980.6753472222</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2369" t="n">
         <v>3120</v>
@@ -62608,6 +62608,32 @@
         <v>161</v>
       </c>
       <c r="H2369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" s="1" t="n">
+        <v>45981.478599537</v>
+      </c>
+      <c r="B2370" t="n">
+        <v>6360</v>
+      </c>
+      <c r="C2370" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2370" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E2370" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2370" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2370" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2370" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62613,7 +62613,7 @@
     </row>
     <row r="2370">
       <c r="A2370" s="1" t="n">
-        <v>45981.478599537</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2370" t="n">
         <v>6360</v>
@@ -62634,6 +62634,32 @@
         <v>161</v>
       </c>
       <c r="H2370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" s="1" t="n">
+        <v>45982.5743287037</v>
+      </c>
+      <c r="B2371" t="n">
+        <v>8520</v>
+      </c>
+      <c r="C2371" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="D2371" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="E2371" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2371" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2371" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2371" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62639,7 +62639,7 @@
     </row>
     <row r="2371">
       <c r="A2371" s="1" t="n">
-        <v>45982.5743287037</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2371" t="n">
         <v>8520</v>
@@ -62660,6 +62660,32 @@
         <v>161</v>
       </c>
       <c r="H2371" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="1" t="n">
+        <v>45985.5776851852</v>
+      </c>
+      <c r="B2372" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2372" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2372" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E2372" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2372" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2372" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2372" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62665,7 +62665,7 @@
     </row>
     <row r="2372">
       <c r="A2372" s="1" t="n">
-        <v>45985.5776851852</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2372" t="n">
         <v>120</v>
@@ -62686,6 +62686,32 @@
         <v>161</v>
       </c>
       <c r="H2372" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" s="1" t="n">
+        <v>45986.359212963</v>
+      </c>
+      <c r="B2373" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2373" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D2373" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E2373" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F2373" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2373" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2373" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -682,6 +682,9 @@
   <si>
     <t xml:space="preserve">4.34000015258789</t>
   </si>
+  <si>
+    <t xml:space="preserve">4.55999994277954</t>
+  </si>
 </sst>
 </file>
 
@@ -62691,7 +62694,7 @@
     </row>
     <row r="2373">
       <c r="A2373" s="1" t="n">
-        <v>45986.359212963</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2373" t="n">
         <v>1200</v>
@@ -62712,6 +62715,32 @@
         <v>161</v>
       </c>
       <c r="H2373" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="1" t="n">
+        <v>45987.661712963</v>
+      </c>
+      <c r="B2374" t="n">
+        <v>54000</v>
+      </c>
+      <c r="C2374" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2374" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="E2374" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2374" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2374" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2374" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62720,7 +62720,7 @@
     </row>
     <row r="2374">
       <c r="A2374" s="1" t="n">
-        <v>45987.661712963</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2374" t="n">
         <v>54000</v>
@@ -62741,6 +62741,32 @@
         <v>223</v>
       </c>
       <c r="H2374" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" s="1" t="n">
+        <v>45988.5700231481</v>
+      </c>
+      <c r="B2375" t="n">
+        <v>13440</v>
+      </c>
+      <c r="C2375" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2375" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2375" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2375" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2375" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2375" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -685,6 +685,9 @@
   <si>
     <t xml:space="preserve">4.55999994277954</t>
   </si>
+  <si>
+    <t xml:space="preserve">4.57999992370605</t>
+  </si>
 </sst>
 </file>
 
@@ -62746,7 +62749,7 @@
     </row>
     <row r="2375">
       <c r="A2375" s="1" t="n">
-        <v>45988.5700231481</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2375" t="n">
         <v>13440</v>
@@ -62767,6 +62770,32 @@
         <v>163</v>
       </c>
       <c r="H2375" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" s="1" t="n">
+        <v>45989.6363773148</v>
+      </c>
+      <c r="B2376" t="n">
+        <v>3960</v>
+      </c>
+      <c r="C2376" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2376" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2376" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2376" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2376" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2376" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62775,7 +62775,7 @@
     </row>
     <row r="2376">
       <c r="A2376" s="1" t="n">
-        <v>45989.6363773148</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2376" t="n">
         <v>3960</v>
@@ -62796,6 +62796,32 @@
         <v>224</v>
       </c>
       <c r="H2376" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" s="1" t="n">
+        <v>45992.3916550926</v>
+      </c>
+      <c r="B2377" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2377" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2377" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2377" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2377" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2377" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2377" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62801,7 +62801,7 @@
     </row>
     <row r="2377">
       <c r="A2377" s="1" t="n">
-        <v>45992.3916550926</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2377" t="n">
         <v>1200</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62825,6 +62825,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2378">
+      <c r="A2378" s="1" t="n">
+        <v>45993.3333333333</v>
+      </c>
+      <c r="B2378" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2378" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2378" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2378" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2378" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2378" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2378" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62851,6 +62851,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2379">
+      <c r="A2379" s="1" t="n">
+        <v>45994.3333333333</v>
+      </c>
+      <c r="B2379" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2379" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2379" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2379" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2379" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2379" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2379" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" s="1" t="n">
+        <v>45995.6802893518</v>
+      </c>
+      <c r="B2380" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2380" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2380" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2380" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2380" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2380" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2380" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62879,7 +62879,7 @@
     </row>
     <row r="2380">
       <c r="A2380" s="1" t="n">
-        <v>45995.6802893518</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2380" t="n">
         <v>1800</v>
@@ -62900,6 +62900,32 @@
         <v>223</v>
       </c>
       <c r="H2380" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" s="1" t="n">
+        <v>45996.4783564815</v>
+      </c>
+      <c r="B2381" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C2381" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2381" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2381" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2381" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2381" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2381" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62905,7 +62905,7 @@
     </row>
     <row r="2381">
       <c r="A2381" s="1" t="n">
-        <v>45996.4783564815</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2381" t="n">
         <v>1680</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62929,6 +62929,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2382">
+      <c r="A2382" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B2382" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2382" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2382" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2382" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2382" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2382" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2382" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62955,6 +62955,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2383">
+      <c r="A2383" s="1" t="n">
+        <v>46000.3333333333</v>
+      </c>
+      <c r="B2383" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2383" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2383" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2383" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2383" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2383" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2383" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" s="1" t="n">
+        <v>46001.4915277778</v>
+      </c>
+      <c r="B2384" t="n">
+        <v>9960</v>
+      </c>
+      <c r="C2384" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2384" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="E2384" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2384" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="G2384" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2384" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -62983,7 +62983,7 @@
     </row>
     <row r="2384">
       <c r="A2384" s="1" t="n">
-        <v>46001.4915277778</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2384" t="n">
         <v>9960</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63007,6 +63007,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2385">
+      <c r="A2385" s="1" t="n">
+        <v>46002.3333333333</v>
+      </c>
+      <c r="B2385" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2385" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="D2385" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="E2385" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="F2385" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="G2385" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2385" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63033,6 +63033,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2386">
+      <c r="A2386" s="1" t="n">
+        <v>46003.3333333333</v>
+      </c>
+      <c r="B2386" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2386" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="D2386" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="E2386" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="F2386" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="G2386" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" s="1" t="n">
+        <v>46006.3336689815</v>
+      </c>
+      <c r="B2387" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2387" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2387" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2387" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2387" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2387" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2387" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63061,7 +63061,7 @@
     </row>
     <row r="2387">
       <c r="A2387" s="1" t="n">
-        <v>46006.3336689815</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2387" t="n">
         <v>600</v>
@@ -63082,6 +63082,32 @@
         <v>163</v>
       </c>
       <c r="H2387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" s="1" t="n">
+        <v>46007.3343981481</v>
+      </c>
+      <c r="B2388" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2388" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2388" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2388" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2388" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2388" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2388" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63087,7 +63087,7 @@
     </row>
     <row r="2388">
       <c r="A2388" s="1" t="n">
-        <v>46007.3343981481</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2388" t="n">
         <v>120</v>
@@ -63108,6 +63108,32 @@
         <v>163</v>
       </c>
       <c r="H2388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" s="1" t="n">
+        <v>46008.663125</v>
+      </c>
+      <c r="B2389" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C2389" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2389" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2389" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2389" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2389" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2389" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63113,7 +63113,7 @@
     </row>
     <row r="2389">
       <c r="A2389" s="1" t="n">
-        <v>46008.663125</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2389" t="n">
         <v>1080</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63137,6 +63137,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2390">
+      <c r="A2390" s="1" t="n">
+        <v>46009.3333333333</v>
+      </c>
+      <c r="B2390" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2390" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D2390" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2390" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2390" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2390" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" s="1" t="n">
+        <v>46010.5654166667</v>
+      </c>
+      <c r="B2391" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2391" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2391" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2391" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2391" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2391" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2391" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63165,7 +63165,7 @@
     </row>
     <row r="2391">
       <c r="A2391" s="1" t="n">
-        <v>46010.5654166667</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2391" t="n">
         <v>360</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63189,6 +63189,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2392">
+      <c r="A2392" s="1" t="n">
+        <v>46013.3333333333</v>
+      </c>
+      <c r="B2392" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2392" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2392" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2392" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2392" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2392" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2392" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63215,6 +63215,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2393">
+      <c r="A2393" s="1" t="n">
+        <v>46014.3333333333</v>
+      </c>
+      <c r="B2393" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2393" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2393" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2393" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2393" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2393" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2393" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63241,6 +63241,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2394">
+      <c r="A2394" s="1" t="n">
+        <v>46020.3333333333</v>
+      </c>
+      <c r="B2394" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2394" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2394" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2394" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2394" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2394" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2394" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63267,6 +63267,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2395">
+      <c r="A2395" s="1" t="n">
+        <v>46021.3333333333</v>
+      </c>
+      <c r="B2395" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2395" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2395" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2395" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2395" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2395" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2395" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63293,6 +63293,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2396">
+      <c r="A2396" s="1" t="n">
+        <v>46024.3333333333</v>
+      </c>
+      <c r="B2396" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2396" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2396" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2396" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2396" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2396" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" s="1" t="n">
+        <v>46027.3338078704</v>
+      </c>
+      <c r="B2397" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2397" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2397" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2397" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2397" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2397" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63321,7 +63321,7 @@
     </row>
     <row r="2397">
       <c r="A2397" s="1" t="n">
-        <v>46027.3338078704</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2397" t="n">
         <v>1200</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63345,6 +63345,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2398">
+      <c r="A2398" s="1" t="n">
+        <v>46028.3333333333</v>
+      </c>
+      <c r="B2398" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2398" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2398" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2398" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2398" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2398" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2398" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63371,6 +63371,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2399">
+      <c r="A2399" s="1" t="n">
+        <v>46029.3333333333</v>
+      </c>
+      <c r="B2399" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2399" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2399" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2399" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2399" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2399" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2399" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63397,6 +63397,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2400">
+      <c r="A2400" s="1" t="n">
+        <v>46030.3333333333</v>
+      </c>
+      <c r="B2400" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2400" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2400" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2400" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2400" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2400" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2400" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" s="1" t="n">
+        <v>46031.3379050926</v>
+      </c>
+      <c r="B2401" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C2401" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="D2401" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="E2401" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F2401" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G2401" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2401" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63425,7 +63425,7 @@
     </row>
     <row r="2401">
       <c r="A2401" s="1" t="n">
-        <v>46031.3379050926</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2401" t="n">
         <v>2280</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63449,6 +63449,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2402">
+      <c r="A2402" s="1" t="n">
+        <v>46034.3333333333</v>
+      </c>
+      <c r="B2402" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2402" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="D2402" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="E2402" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F2402" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G2402" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2402" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63475,6 +63475,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2403">
+      <c r="A2403" s="1" t="n">
+        <v>46035.3333333333</v>
+      </c>
+      <c r="B2403" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2403" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="D2403" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="E2403" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F2403" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G2403" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2403" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="1" t="n">
+        <v>46036.662037037</v>
+      </c>
+      <c r="B2404" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C2404" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="D2404" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2404" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2404" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G2404" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2404" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63503,7 +63503,7 @@
     </row>
     <row r="2404">
       <c r="A2404" s="1" t="n">
-        <v>46036.662037037</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2404" t="n">
         <v>2280</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63527,6 +63527,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2405">
+      <c r="A2405" s="1" t="n">
+        <v>46037.3333333333</v>
+      </c>
+      <c r="B2405" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2405" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="D2405" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="E2405" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F2405" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G2405" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2405" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="1" t="n">
+        <v>46038.6212847222</v>
+      </c>
+      <c r="B2406" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C2406" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2406" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2406" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2406" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2406" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2406" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63555,7 +63555,7 @@
     </row>
     <row r="2406">
       <c r="A2406" s="1" t="n">
-        <v>46038.6212847222</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2406" t="n">
         <v>7200</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63579,6 +63579,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2407">
+      <c r="A2407" s="1" t="n">
+        <v>46041.3333333333</v>
+      </c>
+      <c r="B2407" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2407" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2407" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2407" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2407" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2407" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2407" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" s="1" t="n">
+        <v>46042.6911458333</v>
+      </c>
+      <c r="B2408" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C2408" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2408" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2408" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2408" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2408" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2408" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63607,7 +63607,7 @@
     </row>
     <row r="2408">
       <c r="A2408" s="1" t="n">
-        <v>46042.6911458333</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2408" t="n">
         <v>3600</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63631,6 +63631,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2409">
+      <c r="A2409" s="1" t="n">
+        <v>46043.3333333333</v>
+      </c>
+      <c r="B2409" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2409" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2409" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2409" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2409" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2409" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2409" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63657,6 +63657,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2410">
+      <c r="A2410" s="1" t="n">
+        <v>46044.3333333333</v>
+      </c>
+      <c r="B2410" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2410" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2410" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2410" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2410" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2410" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2410" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" s="1" t="n">
+        <v>46045.5096527778</v>
+      </c>
+      <c r="B2411" t="n">
+        <v>10680</v>
+      </c>
+      <c r="C2411" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2411" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2411" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2411" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2411" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2411" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63685,7 +63685,7 @@
     </row>
     <row r="2411">
       <c r="A2411" s="1" t="n">
-        <v>46045.5096527778</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2411" t="n">
         <v>10680</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63709,6 +63709,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2412">
+      <c r="A2412" s="1" t="n">
+        <v>46048.3333333333</v>
+      </c>
+      <c r="B2412" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2412" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2412" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2412" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2412" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2412" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2412" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63735,6 +63735,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2413">
+      <c r="A2413" s="1" t="n">
+        <v>46049.3333333333</v>
+      </c>
+      <c r="B2413" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2413" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2413" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2413" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2413" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2413" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2413" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63761,6 +63761,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2414">
+      <c r="A2414" s="1" t="n">
+        <v>46050.3333333333</v>
+      </c>
+      <c r="B2414" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2414" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2414" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2414" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2414" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2414" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2414" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="1" t="n">
+        <v>46051.3989930556</v>
+      </c>
+      <c r="B2415" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2415" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2415" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2415" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2415" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2415" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2415" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63789,7 +63789,7 @@
     </row>
     <row r="2415">
       <c r="A2415" s="1" t="n">
-        <v>46051.3989930556</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2415" t="n">
         <v>120</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63813,6 +63813,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2416">
+      <c r="A2416" s="1" t="n">
+        <v>46052.3333333333</v>
+      </c>
+      <c r="B2416" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2416" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2416" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2416" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2416" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2416" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2416" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63839,6 +63839,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2417">
+      <c r="A2417" s="1" t="n">
+        <v>46055.3333333333</v>
+      </c>
+      <c r="B2417" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2417" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2417" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2417" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2417" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2417" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2417" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="1" t="n">
+        <v>46056.4201851852</v>
+      </c>
+      <c r="B2418" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C2418" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2418" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2418" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2418" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2418" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2418" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63867,7 +63867,7 @@
     </row>
     <row r="2418">
       <c r="A2418" s="1" t="n">
-        <v>46056.4201851852</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B2418" t="n">
         <v>21000</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63891,6 +63891,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2419">
+      <c r="A2419" s="1" t="n">
+        <v>46057.3333333333</v>
+      </c>
+      <c r="B2419" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2419" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2419" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2419" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2419" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2419" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2419" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63917,6 +63917,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2420">
+      <c r="A2420" s="1" t="n">
+        <v>46058.3333333333</v>
+      </c>
+      <c r="B2420" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2420" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2420" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2420" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2420" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2420" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" s="1" t="n">
+        <v>46059.4648842593</v>
+      </c>
+      <c r="B2421" t="n">
+        <v>960</v>
+      </c>
+      <c r="C2421" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2421" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2421" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2421" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2421" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2421" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63945,7 +63945,7 @@
     </row>
     <row r="2421">
       <c r="A2421" s="1" t="n">
-        <v>46059.4648842593</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2421" t="n">
         <v>960</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63969,6 +63969,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2422">
+      <c r="A2422" s="1" t="n">
+        <v>46062.3333333333</v>
+      </c>
+      <c r="B2422" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2422" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2422" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2422" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2422" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2422" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" s="1" t="n">
+        <v>46063.6678703704</v>
+      </c>
+      <c r="B2423" t="n">
+        <v>480</v>
+      </c>
+      <c r="C2423" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2423" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2423" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2423" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2423" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2423" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -63997,7 +63997,7 @@
     </row>
     <row r="2423">
       <c r="A2423" s="1" t="n">
-        <v>46063.6678703704</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2423" t="n">
         <v>480</v>
@@ -64018,6 +64018,32 @@
         <v>224</v>
       </c>
       <c r="H2423" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="1" t="n">
+        <v>46064.4721412037</v>
+      </c>
+      <c r="B2424" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2424" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2424" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2424" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2424" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2424" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2424" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64023,7 +64023,7 @@
     </row>
     <row r="2424">
       <c r="A2424" s="1" t="n">
-        <v>46064.4721412037</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B2424" t="n">
         <v>4800</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64047,6 +64047,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2425">
+      <c r="A2425" s="1" t="n">
+        <v>46065.3333333333</v>
+      </c>
+      <c r="B2425" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2425" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2425" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2425" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2425" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2425" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2425" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" s="1" t="n">
+        <v>46066.6712268519</v>
+      </c>
+      <c r="B2426" t="n">
+        <v>18720</v>
+      </c>
+      <c r="C2426" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2426" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="E2426" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F2426" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2426" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2426" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64075,7 +64075,7 @@
     </row>
     <row r="2426">
       <c r="A2426" s="1" t="n">
-        <v>46066.6712268519</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B2426" t="n">
         <v>18720</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64099,6 +64099,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2427">
+      <c r="A2427" s="1" t="n">
+        <v>46069.3333333333</v>
+      </c>
+      <c r="B2427" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2427" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2427" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2427" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2427" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2427" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2427" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64125,6 +64125,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2428">
+      <c r="A2428" s="1" t="n">
+        <v>46070.3333333333</v>
+      </c>
+      <c r="B2428" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2428" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2428" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2428" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2428" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2428" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2428" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" s="1" t="n">
+        <v>46071.6705092593</v>
+      </c>
+      <c r="B2429" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C2429" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2429" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2429" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2429" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2429" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2429" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64153,7 +64153,7 @@
     </row>
     <row r="2429">
       <c r="A2429" s="1" t="n">
-        <v>46071.6705092593</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2429" t="n">
         <v>2280</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64177,6 +64177,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2430">
+      <c r="A2430" s="1" t="n">
+        <v>46072.3333333333</v>
+      </c>
+      <c r="B2430" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2430" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2430" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2430" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64203,6 +64203,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2431">
+      <c r="A2431" s="1" t="n">
+        <v>46073.3333333333</v>
+      </c>
+      <c r="B2431" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2431" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2431" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2431" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="1" t="n">
+        <v>46076.6270949074</v>
+      </c>
+      <c r="B2432" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C2432" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2432" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2432" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64231,7 +64231,7 @@
     </row>
     <row r="2432">
       <c r="A2432" s="1" t="n">
-        <v>46076.6270949074</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B2432" t="n">
         <v>2280</v>
@@ -64252,6 +64252,32 @@
         <v>223</v>
       </c>
       <c r="H2432" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" s="1" t="n">
+        <v>46077.4029861111</v>
+      </c>
+      <c r="B2433" t="n">
+        <v>720</v>
+      </c>
+      <c r="C2433" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2433" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2433" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2433" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2433" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2433" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64257,7 +64257,7 @@
     </row>
     <row r="2433">
       <c r="A2433" s="1" t="n">
-        <v>46077.4029861111</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B2433" t="n">
         <v>720</v>
@@ -64278,6 +64278,32 @@
         <v>223</v>
       </c>
       <c r="H2433" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="1" t="n">
+        <v>46078.6683449074</v>
+      </c>
+      <c r="B2434" t="n">
+        <v>480</v>
+      </c>
+      <c r="C2434" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2434" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2434" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2434" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2434" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2434" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64283,7 +64283,7 @@
     </row>
     <row r="2434">
       <c r="A2434" s="1" t="n">
-        <v>46078.6683449074</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2434" t="n">
         <v>480</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64307,6 +64307,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2435">
+      <c r="A2435" s="1" t="n">
+        <v>46079.3333333333</v>
+      </c>
+      <c r="B2435" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2435" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2435" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2435" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64333,6 +64333,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2436">
+      <c r="A2436" s="1" t="n">
+        <v>46080.3333333333</v>
+      </c>
+      <c r="B2436" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2436" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2436" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2436" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2436" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2436" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2436" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64359,6 +64359,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2437">
+      <c r="A2437" s="1" t="n">
+        <v>46083.3333333333</v>
+      </c>
+      <c r="B2437" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2437" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2437" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2437" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2437" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2437" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2437" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="1" t="n">
+        <v>46084.6780787037</v>
+      </c>
+      <c r="B2438" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C2438" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="G2438" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2438" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64387,7 +64387,7 @@
     </row>
     <row r="2438">
       <c r="A2438" s="1" t="n">
-        <v>46084.6780787037</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2438" t="n">
         <v>2280</v>
@@ -64408,6 +64408,32 @@
         <v>223</v>
       </c>
       <c r="H2438" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" s="1" t="n">
+        <v>46085.3715740741</v>
+      </c>
+      <c r="B2439" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2439" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2439" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2439" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2439" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2439" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64413,7 +64413,7 @@
     </row>
     <row r="2439">
       <c r="A2439" s="1" t="n">
-        <v>46085.3715740741</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B2439" t="n">
         <v>360</v>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64437,6 +64437,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2440">
+      <c r="A2440" s="1" t="n">
+        <v>46086.3333333333</v>
+      </c>
+      <c r="B2440" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2440" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2440" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2440" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64463,6 +64463,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2441">
+      <c r="A2441" s="1" t="n">
+        <v>46087.3333333333</v>
+      </c>
+      <c r="B2441" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2441" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2441" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2441" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2441" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2441" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64489,6 +64489,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2442">
+      <c r="A2442" s="1" t="n">
+        <v>46090.3333333333</v>
+      </c>
+      <c r="B2442" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2442" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2442" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2442" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2442" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2442" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64515,6 +64515,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2443">
+      <c r="A2443" s="1" t="n">
+        <v>46091.3333333333</v>
+      </c>
+      <c r="B2443" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2443" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2443" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2443" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2443" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2443" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64541,6 +64541,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2444">
+      <c r="A2444" s="1" t="n">
+        <v>46092.3333333333</v>
+      </c>
+      <c r="B2444" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2444" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2444" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2444" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2444" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2444" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64567,6 +64567,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2445">
+      <c r="A2445" s="1" t="n">
+        <v>46093.3333333333</v>
+      </c>
+      <c r="B2445" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2445" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2445" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2445" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64593,6 +64593,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2446">
+      <c r="A2446" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2446" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2446" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2446" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2446" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2446" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2446" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64619,6 +64619,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2447">
+      <c r="A2447" s="1" t="n">
+        <v>46097.3333333333</v>
+      </c>
+      <c r="B2447" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2447" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2447" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2447" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2447" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2447" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64645,6 +64645,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2448">
+      <c r="A2448" s="1" t="n">
+        <v>46098.3333333333</v>
+      </c>
+      <c r="B2448" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2448" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2448" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2448" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2448" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2448" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2448" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -688,6 +688,9 @@
   <si>
     <t xml:space="preserve">4.57999992370605</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
 </sst>
 </file>
 
@@ -64671,6 +64674,82 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2449">
+      <c r="A2449" s="1" t="n">
+        <v>46099.3333333333</v>
+      </c>
+      <c r="B2449" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2449" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2449" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2449" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="1" t="n">
+        <v>46100.3333333333</v>
+      </c>
+      <c r="B2450" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2450" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2450" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2450" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2450"/>
+      <c r="G2450" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2450" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" s="1" t="n">
+        <v>46100.6102893519</v>
+      </c>
+      <c r="B2451" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2451" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2451" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2451" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2451" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64716,9 +64716,11 @@
       <c r="E2450" t="n">
         <v>4.59999990463257</v>
       </c>
-      <c r="F2450"/>
+      <c r="F2450" t="n">
+        <v>4.59999990463257</v>
+      </c>
       <c r="G2450" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -64726,27 +64728,51 @@
     </row>
     <row r="2451">
       <c r="A2451" s="1" t="n">
-        <v>46100.6102893519</v>
+        <v>46101.3333333333</v>
       </c>
       <c r="B2451" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="C2451" t="n">
         <v>4.59999990463257</v>
       </c>
       <c r="D2451" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2451"/>
+      <c r="G2451" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2451" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="1" t="n">
+        <v>46101.5089930556</v>
+      </c>
+      <c r="B2452" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2452" t="n">
         <v>4.59999990463257</v>
       </c>
-      <c r="E2451" t="n">
+      <c r="D2452" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2452" t="n">
         <v>4.59999990463257</v>
       </c>
-      <c r="F2451" t="n">
-        <v>4.59999990463257</v>
-      </c>
-      <c r="G2451" t="s">
+      <c r="G2452" t="s">
         <v>168</v>
       </c>
-      <c r="H2451" t="s">
+      <c r="H2452" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -688,9 +688,6 @@
   <si>
     <t xml:space="preserve">4.57999992370605</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
 </sst>
 </file>
 
@@ -64742,37 +64739,13 @@
       <c r="E2451" t="n">
         <v>4.55999994277954</v>
       </c>
-      <c r="F2451"/>
+      <c r="F2451" t="n">
+        <v>4.59999990463257</v>
+      </c>
       <c r="G2451" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="H2451" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2452">
-      <c r="A2452" s="1" t="n">
-        <v>46101.5089930556</v>
-      </c>
-      <c r="B2452" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C2452" t="n">
-        <v>4.59999990463257</v>
-      </c>
-      <c r="D2452" t="n">
-        <v>4.55999994277954</v>
-      </c>
-      <c r="E2452" t="n">
-        <v>4.55999994277954</v>
-      </c>
-      <c r="F2452" t="n">
-        <v>4.59999990463257</v>
-      </c>
-      <c r="G2452" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2452" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64749,6 +64749,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2452">
+      <c r="A2452" s="1" t="n">
+        <v>46104.3333333333</v>
+      </c>
+      <c r="B2452" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2452" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2452" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2452" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -688,6 +688,9 @@
   <si>
     <t xml:space="preserve">4.57999992370605</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
 </sst>
 </file>
 
@@ -64775,6 +64778,82 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2453">
+      <c r="A2453" s="1" t="n">
+        <v>46105.3333333333</v>
+      </c>
+      <c r="B2453" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2453" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2453" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2453" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2453" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2453" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2453" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="1" t="n">
+        <v>46106.3333333333</v>
+      </c>
+      <c r="B2454" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C2454" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2454" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2454" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2454"/>
+      <c r="G2454" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2454" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" s="1" t="n">
+        <v>46106.6490046296</v>
+      </c>
+      <c r="B2455" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2455" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2455" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -688,9 +688,6 @@
   <si>
     <t xml:space="preserve">4.57999992370605</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
 </sst>
 </file>
 
@@ -64820,37 +64817,13 @@
       <c r="E2454" t="n">
         <v>4.55999994277954</v>
       </c>
-      <c r="F2454"/>
+      <c r="F2454" t="n">
+        <v>4.57999992370605</v>
+      </c>
       <c r="G2454" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H2454" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2455">
-      <c r="A2455" s="1" t="n">
-        <v>46106.6490046296</v>
-      </c>
-      <c r="B2455" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C2455" t="n">
-        <v>4.59999990463257</v>
-      </c>
-      <c r="D2455" t="n">
-        <v>4.55999994277954</v>
-      </c>
-      <c r="E2455" t="n">
-        <v>4.55999994277954</v>
-      </c>
-      <c r="F2455" t="n">
-        <v>4.57999992370605</v>
-      </c>
-      <c r="G2455" t="s">
-        <v>224</v>
-      </c>
-      <c r="H2455" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64827,6 +64827,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2455">
+      <c r="A2455" s="1" t="n">
+        <v>46107.3333333333</v>
+      </c>
+      <c r="B2455" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2455" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2455" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64853,6 +64853,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2456">
+      <c r="A2456" s="1" t="n">
+        <v>46108.3333333333</v>
+      </c>
+      <c r="B2456" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2456" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2456" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2456" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2456" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B2457" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C2457" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2457" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2457" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64905,6 +64905,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2458">
+      <c r="A2458" s="1" t="n">
+        <v>46112.2916666667</v>
+      </c>
+      <c r="B2458" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2458" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2458" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2458" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2458" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2458" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64931,6 +64931,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2459">
+      <c r="A2459" s="1" t="n">
+        <v>46113.2916666667</v>
+      </c>
+      <c r="B2459" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2459" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2459" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2459" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2459" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2459" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64957,6 +64957,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2460">
+      <c r="A2460" s="1" t="n">
+        <v>46114.2916666667</v>
+      </c>
+      <c r="B2460" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2460" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2460" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2460" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2460" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2460" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64983,6 +64983,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2461">
+      <c r="A2461" s="1" t="n">
+        <v>46119.2917361111</v>
+      </c>
+      <c r="B2461" t="n">
+        <v>960</v>
+      </c>
+      <c r="C2461" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2461" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2461" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2461" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2461" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -64985,7 +64985,7 @@
     </row>
     <row r="2461">
       <c r="A2461" s="1" t="n">
-        <v>46119.2917361111</v>
+        <v>46119.2916666667</v>
       </c>
       <c r="B2461" t="n">
         <v>960</v>
@@ -65006,6 +65006,32 @@
         <v>224</v>
       </c>
       <c r="H2461" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="1" t="n">
+        <v>46120.2916666667</v>
+      </c>
+      <c r="B2462" t="n">
+        <v>1440</v>
+      </c>
+      <c r="C2462" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2462" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2462" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2462" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2462" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65035,6 +65035,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2463">
+      <c r="A2463" s="1" t="n">
+        <v>46121.2916666667</v>
+      </c>
+      <c r="B2463" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2463" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2463" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2463" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2463" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2463" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2463" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65061,6 +65061,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2464">
+      <c r="A2464" s="1" t="n">
+        <v>46122.2916666667</v>
+      </c>
+      <c r="B2464" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2464" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2464" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2464" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2464" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2464" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2464" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" s="1" t="n">
+        <v>46125.2916666667</v>
+      </c>
+      <c r="B2465" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C2465" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2465" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2465" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2465" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2465" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2465" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65113,6 +65113,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2466">
+      <c r="A2466" s="1" t="n">
+        <v>46126.2916666667</v>
+      </c>
+      <c r="B2466" t="n">
+        <v>720</v>
+      </c>
+      <c r="C2466" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2466" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2466" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2466" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2466" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2466" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65139,6 +65139,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2467">
+      <c r="A2467" s="1" t="n">
+        <v>46127.2916666667</v>
+      </c>
+      <c r="B2467" t="n">
+        <v>240</v>
+      </c>
+      <c r="C2467" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2467" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2467" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2467" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2467" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2467" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65165,6 +65165,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2468">
+      <c r="A2468" s="1" t="n">
+        <v>46128.2916666667</v>
+      </c>
+      <c r="B2468" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2468" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2468" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2468" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2468" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2468" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2468" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" s="1" t="n">
+        <v>46129.2916666667</v>
+      </c>
+      <c r="B2469" t="n">
+        <v>960</v>
+      </c>
+      <c r="C2469" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2469" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2469" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2469" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2469" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2469" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65217,6 +65217,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2470">
+      <c r="A2470" s="1" t="n">
+        <v>46132.2916666667</v>
+      </c>
+      <c r="B2470" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2470" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2470" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2470" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2470" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2470" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2470" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65243,6 +65243,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2471">
+      <c r="A2471" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B2471" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C2471" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2471" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2471" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2471" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2471" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2471" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65269,6 +65269,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2472">
+      <c r="A2472" s="1" t="n">
+        <v>46134.2916666667</v>
+      </c>
+      <c r="B2472" t="n">
+        <v>15960</v>
+      </c>
+      <c r="C2472" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2472" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2472" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2472" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="G2472" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2472" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65277,7 +65277,7 @@
         <v>15960</v>
       </c>
       <c r="C2472" t="n">
-        <v>4.57999992370605</v>
+        <v>4.61999988555908</v>
       </c>
       <c r="D2472" t="n">
         <v>4.57999992370605</v>
@@ -65292,6 +65292,32 @@
         <v>117</v>
       </c>
       <c r="H2472" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" s="1" t="n">
+        <v>46135.2916666667</v>
+      </c>
+      <c r="B2473" t="n">
+        <v>720</v>
+      </c>
+      <c r="C2473" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2473" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2473" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2473" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2473" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2473" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65321,6 +65321,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2474">
+      <c r="A2474" s="1" t="n">
+        <v>46136.2916666667</v>
+      </c>
+      <c r="B2474" t="n">
+        <v>960</v>
+      </c>
+      <c r="C2474" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2474" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E2474" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2474" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G2474" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2474" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65347,6 +65347,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2475">
+      <c r="A2475" s="1" t="n">
+        <v>46139.2916666667</v>
+      </c>
+      <c r="B2475" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2475" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2475" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2475" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2475" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2475" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2475" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65373,6 +65373,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2476">
+      <c r="A2476" s="1" t="n">
+        <v>46140.2916666667</v>
+      </c>
+      <c r="B2476" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2476" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2476" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2476" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2476" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2476" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2476" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65399,6 +65399,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2477">
+      <c r="A2477" s="1" t="n">
+        <v>46141.2916666667</v>
+      </c>
+      <c r="B2477" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2477" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2477" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2477" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2477" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2477" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2477" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" s="1" t="n">
+        <v>46142.2916666667</v>
+      </c>
+      <c r="B2478" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2478" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2478" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2478" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2478" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2478" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2478" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -65451,6 +65451,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2479">
+      <c r="A2479" s="1" t="n">
+        <v>46146.2916666667</v>
+      </c>
+      <c r="B2479" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2479" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2479" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2479" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F2479" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2479" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2479" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCM.MI.xlsx
+++ b/data/SCM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -36,9 +36,6 @@
   </si>
   <si>
     <t xml:space="preserve">ticker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59999990463257</t>
   </si>
   <si>
     <t xml:space="preserve">SCM.MI</t>
@@ -423,11 +420,11 @@
       <c r="F2" t="n">
         <v>4.59999990463257</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="H2" t="s">
         <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
